--- a/speedway-data.xlsx
+++ b/speedway-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keeganmillar/Documents/GitHub/Speedway-GFX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD75762-6C6A-754A-AAB2-EF81143C95C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633F47C1-9727-4E4E-B125-5615AC4F1FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48320" yWindow="5120" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Event Info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="65">
   <si>
     <t>Event Information</t>
   </si>
@@ -80,51 +80,24 @@
     <t>17:00</t>
   </si>
   <si>
-    <t>Ministocks</t>
-  </si>
-  <si>
     <t>Heat 1</t>
   </si>
   <si>
-    <t>10 laps</t>
-  </si>
-  <si>
     <t>Scheduled</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>17:15</t>
   </si>
   <si>
-    <t>Midgets</t>
-  </si>
-  <si>
-    <t>12 laps</t>
-  </si>
-  <si>
     <t>17:30</t>
   </si>
   <si>
-    <t>Street Stocks</t>
-  </si>
-  <si>
-    <t>15 laps</t>
-  </si>
-  <si>
     <t>17:45</t>
   </si>
   <si>
-    <t>Sprintcars</t>
-  </si>
-  <si>
     <t>18:00</t>
   </si>
   <si>
-    <t>Super Saloons</t>
-  </si>
-  <si>
     <t>18:20</t>
   </si>
   <si>
@@ -146,103 +119,103 @@
     <t>19:45</t>
   </si>
   <si>
-    <t>20 laps</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>20:05</t>
   </si>
   <si>
-    <t>25 laps</t>
-  </si>
-  <si>
     <t>20:30</t>
   </si>
   <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
     <t>Heat 3</t>
   </si>
   <si>
-    <t>20:80</t>
-  </si>
-  <si>
-    <t>20:105</t>
-  </si>
-  <si>
-    <t>21:26</t>
-  </si>
-  <si>
-    <t>20:130</t>
-  </si>
-  <si>
-    <t>20:155</t>
-  </si>
-  <si>
-    <t>21:27</t>
-  </si>
-  <si>
-    <t>20:180</t>
-  </si>
-  <si>
-    <t>20:205</t>
-  </si>
-  <si>
-    <t>21:28</t>
-  </si>
-  <si>
-    <t>20:230</t>
-  </si>
-  <si>
-    <t>20:255</t>
-  </si>
-  <si>
-    <t>21:29</t>
-  </si>
-  <si>
-    <t>20:280</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>20:281</t>
-  </si>
-  <si>
-    <t>Rotorua Speedway</t>
-  </si>
-  <si>
     <t>Paradise Valley</t>
   </si>
   <si>
     <t>Hashtag</t>
   </si>
   <si>
-    <t>#Test</t>
-  </si>
-  <si>
-    <t>Keegan Millar</t>
-  </si>
-  <si>
     <t>Matt O'Meeghan</t>
   </si>
   <si>
-    <t>Test Subtitle</t>
-  </si>
-  <si>
-    <t>Middle Test</t>
-  </si>
-  <si>
-    <t>Left Underscore</t>
-  </si>
-  <si>
-    <t>Keegan</t>
+    <t>Thompson Lawnmowers &amp; Chainsaws Ministocks Y Group</t>
+  </si>
+  <si>
+    <t>50 Fifty Traffic Management Stockcars Group 1</t>
+  </si>
+  <si>
+    <t>Chanels Lawnmowing Stockcars Group 2</t>
+  </si>
+  <si>
+    <t>Driftkartz Streetstocks Heat 1</t>
+  </si>
+  <si>
+    <t>MTF Finance Ministocks O Group</t>
+  </si>
+  <si>
+    <t>Sportsweb Photography Superstocks Heat 1</t>
+  </si>
+  <si>
+    <t>Central Auto Dismantlers Stockcars Group 1</t>
+  </si>
+  <si>
+    <t>The ToolShed Stockcars Group 2</t>
+  </si>
+  <si>
+    <t>Sharns with Sparky Streetstocks Heat two</t>
+  </si>
+  <si>
+    <t>Dorrell Flooring Ministocks O Group</t>
+  </si>
+  <si>
+    <t>Goodrick Upholstery Superstocks Heat 2</t>
+  </si>
+  <si>
+    <t>Barclay Engravers Ministocks Y Group</t>
+  </si>
+  <si>
+    <t>Hi Track Contracting Stockcar Feature</t>
+  </si>
+  <si>
+    <t>Fletcher Easy Steel Streetstocks Heat 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawker Trucks Ministocks O Group </t>
+  </si>
+  <si>
+    <t>Morrow Builders Superstocks Heat 3</t>
+  </si>
+  <si>
+    <t>Makita Stockcars Consolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>Baypark Speedway</t>
+  </si>
+  <si>
+    <t>#BayparkSpeedway</t>
+  </si>
+  <si>
+    <t>Sponsor Logo</t>
+  </si>
+  <si>
+    <t>assets/SponsorLogo.png</t>
+  </si>
+  <si>
+    <t>@SharnswithSparky</t>
+  </si>
+  <si>
+    <t>Paul Hickey</t>
+  </si>
+  <si>
+    <t>Commentary</t>
+  </si>
+  <si>
+    <t>Tony G</t>
   </si>
 </sst>
 </file>
@@ -284,8 +257,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,10 +630,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
@@ -670,16 +644,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -753,10 +727,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -773,10 +747,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -793,10 +767,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>
@@ -811,17 +785,17 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 A4:F6 D3:F3 A2:B2 D2:F2 A9 A7 D7:F7 A8 D8:F8 D9:F9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 A4:F6 E3:F3 A2:B2 E2:F2 A9 A7 D7:F7 A8 D8:F8 D9:F9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -844,641 +818,372 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
       <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
+      <c r="D14">
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <v>12</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="D17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" t="s">
-        <v>42</v>
+      <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" t="s">
-        <v>42</v>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G11 A14:E16 A13:B13 G14:G16 A12:B12 D12:E12 D13:E13" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 A14 A13 A12 E12 E13 A2:A11 C2:C11 E3:F11 E14 E2:F2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/speedway-data.xlsx
+++ b/speedway-data.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keeganmillar/Documents/GitHub/Speedway-GFX/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliver/Downloads/SPX_1_3_0_macos64/ASSETS/templates/Speedway GFX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633F47C1-9727-4E4E-B125-5615AC4F1FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74600C2-AF11-394F-A5DC-73217B534559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Event Info" sheetId="1" r:id="rId1"/>
     <sheet name="Schedule" sheetId="2" r:id="rId2"/>
+    <sheet name="Classes" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="52">
   <si>
     <t>Event Information</t>
   </si>
@@ -62,167 +76,128 @@
     <t>Event</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>Feature Race</t>
   </si>
   <si>
-    <t>17:00</t>
+    <t>Hashtag</t>
+  </si>
+  <si>
+    <t>Matt O'Meeghan</t>
+  </si>
+  <si>
+    <t>Sponsor Logo</t>
+  </si>
+  <si>
+    <t>assets/SponsorLogo.png</t>
+  </si>
+  <si>
+    <t>@SharnswithSparky</t>
+  </si>
+  <si>
+    <t>Paul Hickey</t>
+  </si>
+  <si>
+    <t>Commentary</t>
+  </si>
+  <si>
+    <t>Tony G</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Ministocks</t>
+  </si>
+  <si>
+    <t>Stockcars</t>
+  </si>
+  <si>
+    <t>Streetstocks</t>
   </si>
   <si>
     <t>Heat 1</t>
   </si>
   <si>
-    <t>Scheduled</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
     <t>Heat 2</t>
   </si>
   <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>Heat 3</t>
-  </si>
-  <si>
-    <t>Paradise Valley</t>
-  </si>
-  <si>
-    <t>Hashtag</t>
-  </si>
-  <si>
-    <t>Matt O'Meeghan</t>
-  </si>
-  <si>
-    <t>Thompson Lawnmowers &amp; Chainsaws Ministocks Y Group</t>
-  </si>
-  <si>
-    <t>50 Fifty Traffic Management Stockcars Group 1</t>
-  </si>
-  <si>
-    <t>Chanels Lawnmowing Stockcars Group 2</t>
-  </si>
-  <si>
-    <t>Driftkartz Streetstocks Heat 1</t>
-  </si>
-  <si>
-    <t>MTF Finance Ministocks O Group</t>
-  </si>
-  <si>
-    <t>Sportsweb Photography Superstocks Heat 1</t>
-  </si>
-  <si>
-    <t>Central Auto Dismantlers Stockcars Group 1</t>
-  </si>
-  <si>
-    <t>The ToolShed Stockcars Group 2</t>
-  </si>
-  <si>
-    <t>Sharns with Sparky Streetstocks Heat two</t>
-  </si>
-  <si>
-    <t>Dorrell Flooring Ministocks O Group</t>
-  </si>
-  <si>
-    <t>Goodrick Upholstery Superstocks Heat 2</t>
-  </si>
-  <si>
-    <t>Barclay Engravers Ministocks Y Group</t>
-  </si>
-  <si>
-    <t>Hi Track Contracting Stockcar Feature</t>
-  </si>
-  <si>
-    <t>Fletcher Easy Steel Streetstocks Heat 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hawker Trucks Ministocks O Group </t>
-  </si>
-  <si>
-    <t>Morrow Builders Superstocks Heat 3</t>
-  </si>
-  <si>
-    <t>Makita Stockcars Consolation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>TBC</t>
-  </si>
-  <si>
-    <t>Baypark Speedway</t>
+    <t>Saloons</t>
+  </si>
+  <si>
+    <t>Golden Oldies</t>
+  </si>
+  <si>
+    <t>Midgets</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Superstock</t>
+  </si>
+  <si>
+    <t>Super Saloons</t>
+  </si>
+  <si>
+    <t>Mercury Baypark</t>
+  </si>
+  <si>
+    <t>Midget Champs</t>
   </si>
   <si>
     <t>#BayparkSpeedway</t>
   </si>
   <si>
-    <t>Sponsor Logo</t>
-  </si>
-  <si>
-    <t>assets/SponsorLogo.png</t>
-  </si>
-  <si>
-    <t>@SharnswithSparky</t>
-  </si>
-  <si>
-    <t>Paul Hickey</t>
-  </si>
-  <si>
-    <t>Commentary</t>
-  </si>
-  <si>
-    <t>Tony G</t>
+    <t>Laps</t>
+  </si>
+  <si>
+    <t>Heat 10</t>
+  </si>
+  <si>
+    <t>Heat 1 1</t>
+  </si>
+  <si>
+    <t>Heat 12</t>
+  </si>
+  <si>
+    <t>Sprintcar</t>
+  </si>
+  <si>
+    <t>Six Shooter</t>
+  </si>
+  <si>
+    <t>Heat 4</t>
+  </si>
+  <si>
+    <t>Heat 13</t>
+  </si>
+  <si>
+    <t>Heat 14</t>
+  </si>
+  <si>
+    <t>Heat 15</t>
+  </si>
+  <si>
+    <t>Heat 5</t>
+  </si>
+  <si>
+    <t>Semi Main</t>
+  </si>
+  <si>
+    <t>Midget</t>
+  </si>
+  <si>
+    <t>Heat</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -232,6 +207,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -257,9 +239,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,6 +585,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -630,10 +618,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
@@ -644,16 +632,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -727,10 +715,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -747,10 +735,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -767,10 +755,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>
@@ -784,6 +772,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
     <ignoredError sqref="A1:F1 A4:F6 E3:F3 A2:B2 E2:F2 A9 A7 D7:F7 A8 D8:F8 D9:F9" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -792,10 +781,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -803,387 +802,392 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>0.40277777777777801</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
+        <v>30</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>0.40972222222222199</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
       <c r="D7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>0.42361111111111099</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>0.43055555555555602</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
       </c>
       <c r="D9">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
+        <v>30</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>0.44444444444444497</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>0.45138888888888901</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
         <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
       </c>
       <c r="D13">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>0.46527777777777801</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>0.47222222222222299</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
       <c r="D15">
-        <v>12</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>0.48611111111111099</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>12</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-      <c r="G18" t="b">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G1 A14 A13 A12 E12 E13 A2:A11 C2:C11 E3:F11 E14 E2:F2" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412537C9-48F8-2740-A92F-5AE44B052DE4}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/speedway-data.xlsx
+++ b/speedway-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliver/Downloads/SPX_1_3_0_macos64/ASSETS/templates/Speedway GFX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74600C2-AF11-394F-A5DC-73217B534559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5710865-BC69-174F-AB2D-19AD98F3BF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Event Info" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
   <si>
     <t>Event Information</t>
   </si>
@@ -142,55 +142,40 @@
     <t>Mercury Baypark</t>
   </si>
   <si>
-    <t>Midget Champs</t>
-  </si>
-  <si>
     <t>#BayparkSpeedway</t>
   </si>
   <si>
     <t>Laps</t>
   </si>
   <si>
-    <t>Heat 10</t>
-  </si>
-  <si>
-    <t>Heat 1 1</t>
-  </si>
-  <si>
-    <t>Heat 12</t>
-  </si>
-  <si>
     <t>Sprintcar</t>
   </si>
   <si>
-    <t>Six Shooter</t>
-  </si>
-  <si>
     <t>Heat 4</t>
   </si>
   <si>
-    <t>Heat 13</t>
-  </si>
-  <si>
-    <t>Heat 14</t>
-  </si>
-  <si>
-    <t>Heat 15</t>
-  </si>
-  <si>
-    <t>Heat 5</t>
-  </si>
-  <si>
-    <t>Semi Main</t>
-  </si>
-  <si>
-    <t>Midget</t>
-  </si>
-  <si>
     <t>Heat</t>
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Supersaloon</t>
+  </si>
+  <si>
+    <t>Race 1</t>
+  </si>
+  <si>
+    <t>Heat 3</t>
+  </si>
+  <si>
+    <t>Race 2</t>
+  </si>
+  <si>
+    <t>Pole Shuffle - Top 6</t>
+  </si>
+  <si>
+    <t>Race 3</t>
   </si>
 </sst>
 </file>
@@ -634,11 +619,8 @@
       <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -802,10 +784,10 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
         <v>22</v>
@@ -818,11 +800,8 @@
       <c r="A2" s="2">
         <v>0.38194444444444442</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -839,16 +818,16 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -859,16 +838,16 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -879,16 +858,16 @@
         <v>0.40277777777777801</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -899,13 +878,13 @@
         <v>0.40972222222222199</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>41</v>
@@ -919,16 +898,16 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -939,16 +918,16 @@
         <v>0.42361111111111099</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -959,16 +938,16 @@
         <v>0.43055555555555602</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -979,16 +958,16 @@
         <v>0.4375</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -999,16 +978,16 @@
         <v>0.44444444444444497</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1019,13 +998,13 @@
         <v>0.45138888888888901</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>41</v>
@@ -1039,16 +1018,16 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -1059,16 +1038,16 @@
         <v>0.46527777777777801</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -1079,10 +1058,10 @@
         <v>0.47222222222222299</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1099,13 +1078,13 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>41</v>
@@ -1119,16 +1098,16 @@
         <v>0.48611111111111099</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
